--- a/2023-2024/Data og lign/Lysintensitet.xlsx
+++ b/2023-2024/Data og lign/Lysintensitet.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NRGY-chri88mh\Desktop\Undervisning\Undervisningsnoter\2023-2024\Data og lign\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66CE64A-6529-4904-93A9-9DAD4EB6492C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2220" yWindow="2310" windowWidth="21600" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -19,14 +25,14 @@
     <t>Afstand i meter</t>
   </si>
   <si>
-    <t>Lysintensitet i lumen</t>
+    <t>Lysintensitet i lux</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,13 +95,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -133,7 +147,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -167,6 +181,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -201,9 +216,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -376,11 +392,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B87"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -388,7 +404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0.4</v>
       </c>
@@ -396,7 +412,7 @@
         <v>1890.23</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.43</v>
       </c>
@@ -404,7 +420,7 @@
         <v>1598.18</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.46</v>
       </c>
@@ -412,15 +428,15 @@
         <v>1409.05</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.49</v>
       </c>
       <c r="B5">
-        <v>1234.66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1234.6600000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.52</v>
       </c>
@@ -428,23 +444,23 @@
         <v>1108.03</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="B7">
-        <v>974.4299999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>974.43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="B8">
         <v>905.97</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.61</v>
       </c>
@@ -452,7 +468,7 @@
         <v>838.87</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0.64</v>
       </c>
@@ -460,7 +476,7 @@
         <v>763.02</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>0.68</v>
       </c>
@@ -468,7 +484,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>0.71</v>
       </c>
@@ -476,23 +492,23 @@
         <v>609.66</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>0.74</v>
       </c>
       <c r="B13">
-        <v>545.45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>545.45000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>0.77</v>
       </c>
       <c r="B14">
-        <v>512.67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>512.66999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>0.8</v>
       </c>
@@ -500,7 +516,7 @@
         <v>481.55</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>0.83</v>
       </c>
@@ -508,7 +524,7 @@
         <v>391.23</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>0.86</v>
       </c>
@@ -516,7 +532,7 @@
         <v>382.6</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>0.89</v>
       </c>
@@ -524,7 +540,7 @@
         <v>394.82</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>0.92</v>
       </c>
@@ -532,7 +548,7 @@
         <v>349.16</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>0.95</v>
       </c>
@@ -540,7 +556,7 @@
         <v>367.35</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>0.98</v>
       </c>
@@ -548,7 +564,7 @@
         <v>306.32</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1.01</v>
       </c>
@@ -556,7 +572,7 @@
         <v>261.12</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1.04</v>
       </c>
@@ -564,7 +580,7 @@
         <v>287.69</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1.07</v>
       </c>
@@ -572,31 +588,31 @@
         <v>287.32</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="B25">
         <v>222.99</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="B26">
         <v>198.8</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="B27">
         <v>236.04</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1.2</v>
       </c>
@@ -604,7 +620,7 @@
         <v>228.54</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1.23</v>
       </c>
@@ -612,7 +628,7 @@
         <v>203.26</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1.26</v>
       </c>
@@ -620,7 +636,7 @@
         <v>204.77</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1.29</v>
       </c>
@@ -628,15 +644,15 @@
         <v>203.18</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1.32</v>
       </c>
       <c r="B32">
-        <v>138.11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>138.11000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1.35</v>
       </c>
@@ -644,7 +660,7 @@
         <v>214.43</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1.38</v>
       </c>
@@ -652,7 +668,7 @@
         <v>161.88</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1.41</v>
       </c>
@@ -660,15 +676,15 @@
         <v>133.59</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1.44</v>
       </c>
       <c r="B36">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>160.19999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1.47</v>
       </c>
@@ -676,7 +692,7 @@
         <v>132.82</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1.5</v>
       </c>
@@ -684,15 +700,15 @@
         <v>110.88</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1.53</v>
       </c>
       <c r="B39">
-        <v>96.68000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>96.68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1.56</v>
       </c>
@@ -700,7 +716,7 @@
         <v>115.8</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1.59</v>
       </c>
@@ -708,15 +724,15 @@
         <v>156.22</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1.62</v>
       </c>
       <c r="B42">
-        <v>157.11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>157.11000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1.65</v>
       </c>
@@ -724,7 +740,7 @@
         <v>111.05</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1.68</v>
       </c>
@@ -732,15 +748,15 @@
         <v>84.5</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1.72</v>
       </c>
       <c r="B45">
-        <v>92.93000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>92.93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1.75</v>
       </c>
@@ -748,15 +764,15 @@
         <v>91.87</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1.78</v>
       </c>
       <c r="B47">
-        <v>91.56999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>91.57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1.81</v>
       </c>
@@ -764,7 +780,7 @@
         <v>69.3</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1.84</v>
       </c>
@@ -772,15 +788,15 @@
         <v>85.16</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1.87</v>
       </c>
       <c r="B50">
-        <v>78.15000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>78.150000000000006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1.9</v>
       </c>
@@ -788,7 +804,7 @@
         <v>80.55</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1.93</v>
       </c>
@@ -796,15 +812,15 @@
         <v>74.95</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1.96</v>
       </c>
       <c r="B53">
-        <v>85.34999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>85.35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1.99</v>
       </c>
@@ -812,7 +828,7 @@
         <v>89.95</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2.02</v>
       </c>
@@ -820,31 +836,31 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="B56">
         <v>90.05</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2.08</v>
       </c>
       <c r="B57">
-        <v>66.43000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>66.430000000000007</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2.11</v>
       </c>
       <c r="B58">
-        <v>88.40000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>88.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2.14</v>
       </c>
@@ -852,7 +868,7 @@
         <v>30.59</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2.17</v>
       </c>
@@ -860,23 +876,23 @@
         <v>77.14</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="B61">
         <v>83.12</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="B62">
         <v>44.15</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2.27</v>
       </c>
@@ -884,15 +900,15 @@
         <v>59.87</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B64">
         <v>61.07</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2.33</v>
       </c>
@@ -900,15 +916,15 @@
         <v>48.06</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2.36</v>
       </c>
       <c r="B66">
-        <v>19.56</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>19.559999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2.39</v>
       </c>
@@ -916,23 +932,23 @@
         <v>26.88</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2.42</v>
       </c>
       <c r="B68">
-        <v>38.2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>38.200000000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="B69">
-        <v>64.01000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>64.010000000000005</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2.48</v>
       </c>
@@ -940,15 +956,15 @@
         <v>55.29</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="B71">
         <v>53.62</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2.54</v>
       </c>
@@ -956,7 +972,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2.57</v>
       </c>
@@ -964,7 +980,7 @@
         <v>56.04</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2.6</v>
       </c>
@@ -972,7 +988,7 @@
         <v>58.75</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2.63</v>
       </c>
@@ -980,15 +996,15 @@
         <v>53.39</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2.66</v>
       </c>
       <c r="B76">
-        <v>76.04000000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>76.040000000000006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2.69</v>
       </c>
@@ -996,7 +1012,7 @@
         <v>26.51</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2.72</v>
       </c>
@@ -1004,7 +1020,7 @@
         <v>46.53</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2.76</v>
       </c>
@@ -1012,7 +1028,7 @@
         <v>49.11</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2.79</v>
       </c>
@@ -1020,7 +1036,7 @@
         <v>17.93</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2.82</v>
       </c>
@@ -1028,7 +1044,7 @@
         <v>24.43</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2.85</v>
       </c>
@@ -1036,7 +1052,7 @@
         <v>58.8</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2.88</v>
       </c>
@@ -1044,7 +1060,7 @@
         <v>18.95</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2.91</v>
       </c>
@@ -1052,7 +1068,7 @@
         <v>37.57</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2.94</v>
       </c>
@@ -1060,7 +1076,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2.97</v>
       </c>
@@ -1068,7 +1084,7 @@
         <v>54.46</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>3</v>
       </c>
